--- a/docs/oc-mensuales/suministro-de-combustibles/jul-2025.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/jul-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21293,7 +21293,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22147,7 +22147,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22635,7 +22635,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23062,7 +23062,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23550,7 +23550,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24465,7 +24465,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25075,7 +25075,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25563,7 +25563,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25807,7 +25807,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25868,7 +25868,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26112,7 +26112,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26234,7 +26234,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26478,7 +26478,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26539,7 +26539,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26661,7 +26661,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27393,7 +27393,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27515,7 +27515,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27637,7 +27637,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27759,7 +27759,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28003,7 +28003,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28735,7 +28735,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28857,7 +28857,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28918,7 +28918,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29162,7 +29162,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29345,7 +29345,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29406,7 +29406,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29467,7 +29467,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29589,7 +29589,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29955,7 +29955,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30077,7 +30077,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30199,7 +30199,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30321,7 +30321,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30443,7 +30443,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30504,7 +30504,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30565,7 +30565,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30809,7 +30809,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30870,7 +30870,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31053,7 +31053,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31175,7 +31175,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31358,7 +31358,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31602,7 +31602,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -32029,7 +32029,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32090,7 +32090,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32151,7 +32151,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32212,7 +32212,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32456,7 +32456,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32517,7 +32517,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32578,7 +32578,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32700,7 +32700,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32761,7 +32761,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32822,7 +32822,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32944,7 +32944,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33005,7 +33005,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33066,7 +33066,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33127,7 +33127,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33188,7 +33188,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33371,7 +33371,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33432,7 +33432,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33493,7 +33493,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33615,7 +33615,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33676,7 +33676,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33859,7 +33859,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33981,7 +33981,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34042,7 +34042,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34164,7 +34164,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34225,7 +34225,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34347,7 +34347,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34408,7 +34408,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34469,7 +34469,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34591,7 +34591,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34652,7 +34652,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34713,7 +34713,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34774,7 +34774,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34835,7 +34835,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34957,7 +34957,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35018,7 +35018,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35079,7 +35079,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35201,7 +35201,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35262,7 +35262,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35323,7 +35323,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35384,7 +35384,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35445,7 +35445,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35506,7 +35506,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35567,7 +35567,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35628,7 +35628,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35689,7 +35689,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35811,7 +35811,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35872,7 +35872,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35933,7 +35933,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35994,7 +35994,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36055,7 +36055,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36177,7 +36177,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36238,7 +36238,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36299,7 +36299,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36421,7 +36421,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36482,7 +36482,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36543,7 +36543,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36665,7 +36665,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36787,7 +36787,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36848,7 +36848,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36909,7 +36909,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36970,7 +36970,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37031,7 +37031,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37092,7 +37092,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37153,7 +37153,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37275,7 +37275,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37336,7 +37336,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37397,7 +37397,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37519,7 +37519,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37641,7 +37641,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37702,7 +37702,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37763,7 +37763,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37824,7 +37824,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37885,7 +37885,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38007,7 +38007,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38190,7 +38190,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38251,7 +38251,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38434,7 +38434,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38495,7 +38495,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38556,7 +38556,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38617,7 +38617,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38678,7 +38678,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38800,7 +38800,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39105,7 +39105,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39227,7 +39227,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39288,7 +39288,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39349,7 +39349,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39532,7 +39532,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39654,7 +39654,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39715,7 +39715,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39776,7 +39776,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39898,7 +39898,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39959,7 +39959,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40081,7 +40081,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40203,7 +40203,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40264,7 +40264,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40447,7 +40447,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40569,7 +40569,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40813,7 +40813,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40874,7 +40874,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40935,7 +40935,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40996,7 +40996,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41057,7 +41057,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41118,7 +41118,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41179,7 +41179,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41240,7 +41240,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41301,7 +41301,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41362,7 +41362,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41484,7 +41484,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41545,7 +41545,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41606,7 +41606,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41667,7 +41667,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41728,7 +41728,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41789,7 +41789,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41850,7 +41850,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41911,7 +41911,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41972,7 +41972,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42094,7 +42094,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42216,7 +42216,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42277,7 +42277,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42338,7 +42338,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42399,7 +42399,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42460,7 +42460,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42521,7 +42521,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42643,7 +42643,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42704,7 +42704,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42765,7 +42765,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42826,7 +42826,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -42887,7 +42887,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -42948,7 +42948,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43009,7 +43009,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43070,7 +43070,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43131,7 +43131,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43192,7 +43192,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43253,7 +43253,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -43314,7 +43314,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
